--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_サービス別単価・見込量試算_20260909.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_サービス別単価・見込量試算_20260909.xlsx
@@ -12448,7 +12448,7 @@
         </is>
       </c>
       <c r="B19" s="21" t="n">
-        <v>6937.756340090405</v>
+        <v>6682.339026313487</v>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>総費用額3,537,755千円×23％−取崩0千円÷収納率99.35％÷補正後被保険者数9,838人÷12</t>
+          <t>（標準給付費3,330,495＋地域支援事業費207,260）×23％＋（標準給付費＋総合事業費110,960）×（5％−5.963％）−取崩0千円　÷収納率99.35％÷補正後被保険者数9,798人÷12</t>
         </is>
       </c>
     </row>
@@ -12468,7 +12468,7 @@
         </is>
       </c>
       <c r="B20" s="21" t="n">
-        <v>6835.440072224646</v>
+        <v>6579.605257264987</v>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
@@ -12477,7 +12477,7 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>総費用額3,537,755千円×23％−取崩12,000千円÷収納率99.35％÷補正後被保険者数9,838人÷12</t>
+          <t>（標準給付費3,330,495＋地域支援事業費207,260）×23％＋（標準給付費＋総合事業費110,960）×（5％−5.963％）−取崩12,000千円　÷収納率99.35％÷補正後被保険者数9,798人÷12</t>
         </is>
       </c>
     </row>
@@ -12488,7 +12488,7 @@
         </is>
       </c>
       <c r="B21" s="21" t="n">
-        <v>6639.333892148609</v>
+        <v>6382.698866588697</v>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>総費用額3,537,755千円×23％−取崩35,000千円÷収納率99.35％÷補正後被保険者数9,838人÷12</t>
+          <t>（標準給付費3,330,495＋地域支援事業費207,260）×23％＋（標準給付費＋総合事業費110,960）×（5％−5.963％）−取崩35,000千円　÷収納率99.35％÷補正後被保険者数9,798人÷12</t>
         </is>
       </c>
     </row>
@@ -12524,28 +12524,28 @@
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>※ 地域支援事業費は第9期計画の見込み（3年計207,260千円）を仮置きした。実績は未受領。</t>
+          <t>※ 地域支援事業費は第9期計画の見込み（3年計207,260千円、うち総合事業費110,960千円）を仮置きした。実績は未受領。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>※ 第1号被保険者負担割合は第9期と同じ23％。第10期の割合は国の基本指針で示される。</t>
+          <t>※ 第1号被保険者負担割合は第9期と同じ23％。**3年の計画期間ごとに政令で定められるもので、第10期の値は確認を要する。1ptで月額303円。**</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>※ 調整交付金は相当額と見込額が一致する（標準の5％が全額交付される）ものとした。**小野町は後期高齢者加入割合が高く、実際には5％を超える交付が見込まれる。その分だけ保険料は下がる。**</t>
+          <t>**※ 調整交付金は標準給付費と総合事業費にのみかかる（包括的支援事業・任意事業費は対象外）。**見込交付割合は第9期計画の公表値から逆算した小野町の実績値5.963％を置いた。**小野町は後期高齢者加入割合が高く低所得層が厚いため、標準の5％を上回る。**第10期の値は見える化システムの係数シート（全国値）で確認する。1ptで月額295円。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>※ 補正後被保険者数は令和7年度の所得段階別第1号被保険者数（様式1 所得段階別）を3年分としたもの。所得段階の設定が変われば動く。</t>
+          <t>※ 補正後被保険者数は、令和7年度末の所得段階別構成比（様式1 所得段階別）を第10期3年分の第1号被保険者数10,284人に当てたもの。所得段階の設定が変われば動く。</t>
         </is>
       </c>
     </row>
